--- a/backend/bookings.xlsx
+++ b/backend/bookings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,15 +439,20 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Contact Info</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>Details</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -455,11 +460,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:51:38</t>
+          <t>2026-09-09 16:20:28</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -469,20 +474,105 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>abc xyz</t>
+          <t>zzzz mmmm</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>987654321</t>
+          <t>6002323454</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Address: aaa; Medicines: bbbb; Delivery date: 2026-08-27</t>
+          <t>rupankarb1@gmail.com</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
+        <is>
+          <t>Delivery address: majitar; Medicines: llllll; Preferred delivery date: 2026-09-10</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-09-09 17:00:52</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Medicine Delivery</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>lll mmm</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>6002323454</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Delivery address: majitarrr; Medicines: nnnn; Preferred delivery date: 2026-09-14</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-09-11 16:47:06</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Medicine Delivery</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Rupankar Lahon</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>6002323454</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>rupankarb1@gmail.com</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Delivery address: Majitar; Medicines: Paracetamol; Preferred delivery date: 2026-09-10</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>

--- a/backend/bookings.xlsx
+++ b/backend/bookings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,6 +573,46 @@
         </is>
       </c>
       <c r="H4" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-09-21 15:40:03</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Medicine Delivery</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Aman Haz</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>6002323454</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>rupankarb1@gmail.com</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Delivery address: Siliguri; Medicines: nnn; Preferred delivery date: 2026-09-23</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
